--- a/output/tables/2025/metadata_variables.xlsx
+++ b/output/tables/2025/metadata_variables.xlsx
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">Fuente: categorizada</t>
   </si>
   <si>
-    <t xml:space="preserve">emper_ep_pct_rec_tercil</t>
+    <t xml:space="preserve">emper_ep_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Inseguridad en Espacio público (tercile)</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">Entra al modelo (MCA)</t>
   </si>
   <si>
-    <t xml:space="preserve">emper_barrio_pct_rec_tercil</t>
+    <t xml:space="preserve">emper_barrio_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Inseguridad en Barrio (tercile)</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1 = Baja inseguridad en el barrio; 2 = Media inseguridad en el barrio; 3 = Alta inseguridad en el barrio; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
   </si>
   <si>
-    <t xml:space="preserve">emper_casa_pct_rec_tercil</t>
+    <t xml:space="preserve">emper_casa_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Inseguridad en Casa (tercile)</t>
@@ -1319,7 +1319,7 @@
     <t xml:space="preserve">perper_p_expos_delito, perper_p_delito_pronostico_1, perper_p_delito_pronostico_2, perper_p_delito_pronostico_3, perper_p_delito_pronostico_4, perper_p_delito_pronostico_6, perper_p_delito_pronostico_9, perper_p_delito_pronostico_10, perper_p_delito_pronostico_11, perper_p_delito_pronostico_5, perper_p_delito_pronostico_7, perper_p_delito_pronostico_8, perper_p_expos_delito, perper_p_delito_pronostico_77, perper_p_delito_pronostico_88, perper_p_delito_pronostico_99</t>
   </si>
   <si>
-    <t xml:space="preserve">comper_pct_rec_tercil</t>
+    <t xml:space="preserve">comper_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Modifica comportamiento (tercile)</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">0 = No gasta en medidas de seguridad; 1 = Gasta en medidas de seguridad; 88 = No sabe; 99 = No responde</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_per_pct_rec_tercil</t>
+    <t xml:space="preserve">comgen_per_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Dispone de medidas de seguridad (personales) (tercile)</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">1 = Baja disposición de medidas vivienda; 2 = Media disposición de medidas vivienda; 3 = Alta disposición de medidas vivienda; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_com_pct_rec_tercil</t>
+    <t xml:space="preserve">comgen_com_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Disponen de medidas de seguridad (comunitarias) (tercile)</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">C1; C2; C3; C4</t>
   </si>
   <si>
-    <t xml:space="preserve">emper_ep_pct_rec_tercil, emper_barrio_pct_rec_tercil, emper_casa_pct_rec_tercil, perper_delito, comper_pct_rec_tercil, comper_gasto, comgen_per_pct_rec_tercil, comgen_com_pct_rec_tercil</t>
+    <t xml:space="preserve">emper_ep_pct_cat, emper_barrio_pct_cat, emper_casa_pct_cat, perper_delito, comper_pct_cat, comper_gasto, comgen_per_pct_cat, comgen_com_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Resultado del modelo</t>

--- a/output/tables/2025/metadata_variables.xlsx
+++ b/output/tables/2025/metadata_variables.xlsx
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">emper_ep_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Inseguridad en Espacio público (tercile)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = Baja inseguridad en espacio publico; 2 = Media inseguridad en espacio publico; 3 = Alta inseguridad en espacio publico; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
+    <t xml:space="preserve">Inseguridad en espacio público (categorizada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = Sin inseguridad en espacio público; 2 = Inseguridad en hasta la mitad de los lugares; 3 = Inseguridad en más de la mitad de los lugares; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
   </si>
   <si>
     <t xml:space="preserve">Entra al modelo (MCA)</t>
@@ -1295,19 +1295,19 @@
     <t xml:space="preserve">emper_barrio_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Inseguridad en Barrio (tercile)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = Baja inseguridad en el barrio; 2 = Media inseguridad en el barrio; 3 = Alta inseguridad en el barrio; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
+    <t xml:space="preserve">Inseguridad en el barrio (categorizada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = Sin inseguridad en el barrio; 2 = Inseguridad en el barrio, de día o de noche; 3 = Inseguridad en el barrio, de día y de noche; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
   </si>
   <si>
     <t xml:space="preserve">emper_casa_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Inseguridad en Casa (tercile)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = Baja inseguridad en la casa; 2 = Media inseguridad en la casa; 3 = Alta inseguridad en la casa; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
+    <t xml:space="preserve">Inseguridad en la casa (categorizada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = Sin inseguridad en la casa; 2 = Inseguridad en la casa, de día o de noche; 3 = Inseguridad en la casa, de día y de noche; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
   </si>
   <si>
     <t xml:space="preserve">Expectativa de ser victima delito</t>
@@ -1322,10 +1322,10 @@
     <t xml:space="preserve">comper_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Modifica comportamiento (tercile)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = Bajas prácticas de evitación; 2 = Medias prácticas de evitación; 3 = Altas prácticas de evitación; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
+    <t xml:space="preserve">Modificación de prácticas (categorizada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = No modificó prácticas; 2 = Modificó hasta la mitad de las prácticas; 3 = Modificó más de la mitad de las prácticas; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
   </si>
   <si>
     <t xml:space="preserve">Gasta en medidas de seguridad</t>
@@ -1337,19 +1337,19 @@
     <t xml:space="preserve">comgen_per_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Dispone de medidas de seguridad (personales) (tercile)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = Baja disposición de medidas vivienda; 2 = Media disposición de medidas vivienda; 3 = Alta disposición de medidas vivienda; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
+    <t xml:space="preserve">Medidas de seguridad de la vivienda (categorizada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = Sin medidas en la vivienda; 2 = Una o dos medidas en la vivienda; 3 = Tres o más medidas en la vivienda; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
   </si>
   <si>
     <t xml:space="preserve">comgen_com_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Disponen de medidas de seguridad (comunitarias) (tercile)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = Baja adopción de medidas comunitarias; 2 = Media adopción de medidas comunitarias; 3 = Alta adopción de medidas comunitarias; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
+    <t xml:space="preserve">Medidas de seguridad del barrio (categorizada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = Sin medidas en el barrio; 2 = Una medida en el barrio; 3 = Dos o más medidas en el barrio; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster</t>

--- a/output/tables/2025/metadata_variables.xlsx
+++ b/output/tables/2025/metadata_variables.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="485">
   <si>
     <t xml:space="preserve">familia</t>
   </si>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">Indique el o los elementos de seguridad que dispone su vivienda o edificio. Perro u otro animal con fines de protección del inmueble</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_per_pct</t>
+    <t xml:space="preserve">comgen_per_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">comgen_medidas_alarma_privada</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">¿Cuál/es de las siguientes medidas ha adoptado en conjunto a las personas de su barrio / cuadra / block para sentirse más seguros/as? Tenemos un grupo de WhatsApp u otra red</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_com_pct</t>
+    <t xml:space="preserve">comgen_com_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">comgen_vecinos_medidas_vigilancia</t>
@@ -1265,91 +1265,79 @@
     <t xml:space="preserve">comper_p_mod_actividades_1, comper_p_mod_actividades_2, comper_p_mod_actividades_3, comper_p_mod_actividades_4, comper_p_mod_actividades_5, comper_p_mod_actividades_6, comper_p_mod_actividades_7, comper_p_mod_actividades_8, comper_p_mod_actividades_9, comper_p_mod_actividades_10, comper_p_mod_actividades_11, comper_p_mod_actividades_12, comper_p_mod_actividades_13</t>
   </si>
   <si>
-    <t xml:space="preserve">Dispone de medidas de seguridad (personales)</t>
+    <t xml:space="preserve">Fuente: categorizada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emper_ep_pct_cat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en espacio público (categorizada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = Sin inseguridad en espacio público; 2 = Inseguridad en hasta la mitad de los lugares; 3 = Inseguridad en más de la mitad de los lugares; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entra al modelo (MCA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emper_barrio_pct_cat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en el barrio (categorizada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = Sin inseguridad en el barrio; 2 = Inseguridad en el barrio, de día o de noche; 3 = Inseguridad en el barrio, de día y de noche; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emper_casa_pct_cat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en la casa (categorizada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = Sin inseguridad en la casa; 2 = Inseguridad en la casa, de día o de noche; 3 = Inseguridad en la casa, de día y de noche; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expectativa de ser victima delito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = No cree que será victima de delito; 2 = Cree que será victima de delito no violento; 3 = Cree que será victima de delito violento; 4 = No sabe/No responde si cree que será victima de delito; 5 = Cree que será victima de otro tipo de delito; 6 = No sabe/No responde de qué delito será victima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">perper_p_expos_delito, perper_p_delito_pronostico_1, perper_p_delito_pronostico_2, perper_p_delito_pronostico_3, perper_p_delito_pronostico_4, perper_p_delito_pronostico_6, perper_p_delito_pronostico_9, perper_p_delito_pronostico_10, perper_p_delito_pronostico_11, perper_p_delito_pronostico_5, perper_p_delito_pronostico_7, perper_p_delito_pronostico_8, perper_p_expos_delito, perper_p_delito_pronostico_77, perper_p_delito_pronostico_88, perper_p_delito_pronostico_99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comper_pct_cat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modificación de prácticas (categorizada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = No modificó prácticas; 2 = Modificó hasta la mitad de las prácticas; 3 = Modificó más de la mitad de las prácticas; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gasta en medidas de seguridad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 = No gasta en medidas de seguridad; 1 = Gasta en medidas de seguridad; 88 = No sabe; 99 = No responde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medidas de seguridad de la vivienda (categorizada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = Sin medidas en la vivienda; 2 = Una o dos medidas en la vivienda; 3 = Tres o más medidas en la vivienda; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
   </si>
   <si>
     <t xml:space="preserve">comgen_medidas_perro, comgen_medidas_alarma_privada, comgen_medidas_camaras_vigilancia, comgen_medidas_rejas, comgen_medidas_cerco, comgen_medidas_proteccion, comgen_medidas_seguro, comgen_medidas_foco, comgen_medidas_otro</t>
   </si>
   <si>
-    <t xml:space="preserve">Disponen de medidas de seguridad (comunitarias)</t>
+    <t xml:space="preserve">Medidas de seguridad del barrio (categorizada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = Sin medidas en el barrio; 2 = Una medida en el barrio; 3 = Dos o más medidas en el barrio; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
   </si>
   <si>
     <t xml:space="preserve">comgen_vecinos_medidas_whatsapp, comgen_vecinos_medidas_vigilancia, comgen_vecinos_medidas_al_comunit, comgen_vecinos_medidas_coord_pol, comgen_vecinos_medidas_coord_mun, comgen_vecinos_medidas_televig, comgen_vecinos_medidas_privad, comgen_vecinos_medidas_otro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuente: categorizada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emper_ep_pct_cat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inseguridad en espacio público (categorizada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = Sin inseguridad en espacio público; 2 = Inseguridad en hasta la mitad de los lugares; 3 = Inseguridad en más de la mitad de los lugares; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entra al modelo (MCA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emper_barrio_pct_cat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inseguridad en el barrio (categorizada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = Sin inseguridad en el barrio; 2 = Inseguridad en el barrio, de día o de noche; 3 = Inseguridad en el barrio, de día y de noche; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emper_casa_pct_cat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inseguridad en la casa (categorizada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = Sin inseguridad en la casa; 2 = Inseguridad en la casa, de día o de noche; 3 = Inseguridad en la casa, de día y de noche; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expectativa de ser victima delito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = No cree que será victima de delito; 2 = Cree que será victima de delito no violento; 3 = Cree que será victima de delito violento; 4 = No sabe/No responde si cree que será victima de delito; 5 = Cree que será victima de otro tipo de delito; 6 = No sabe/No responde de qué delito será victima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">perper_p_expos_delito, perper_p_delito_pronostico_1, perper_p_delito_pronostico_2, perper_p_delito_pronostico_3, perper_p_delito_pronostico_4, perper_p_delito_pronostico_6, perper_p_delito_pronostico_9, perper_p_delito_pronostico_10, perper_p_delito_pronostico_11, perper_p_delito_pronostico_5, perper_p_delito_pronostico_7, perper_p_delito_pronostico_8, perper_p_expos_delito, perper_p_delito_pronostico_77, perper_p_delito_pronostico_88, perper_p_delito_pronostico_99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comper_pct_cat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modificación de prácticas (categorizada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = No modificó prácticas; 2 = Modificó hasta la mitad de las prácticas; 3 = Modificó más de la mitad de las prácticas; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gasta en medidas de seguridad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 = No gasta en medidas de seguridad; 1 = Gasta en medidas de seguridad; 88 = No sabe; 99 = No responde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comgen_per_pct_cat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medidas de seguridad de la vivienda (categorizada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = Sin medidas en la vivienda; 2 = Una o dos medidas en la vivienda; 3 = Tres o más medidas en la vivienda; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comgen_com_pct_cat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medidas de seguridad del barrio (categorizada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = Sin medidas en el barrio; 2 = Una medida en el barrio; 3 = Dos o más medidas en el barrio; 85 = No aplica; 88 = No sabe; 99 = No responde</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster</t>
@@ -4616,158 +4604,158 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="s">
+      <c r="A133" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C133"/>
-      <c r="D133" t="s">
+      <c r="C133" s="2"/>
+      <c r="D133" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E133" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="F133" t="s">
+      <c r="F133" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="G133" t="s">
+      <c r="G133" s="2" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="B134" t="s">
-        <v>173</v>
+        <v>418</v>
       </c>
       <c r="C134"/>
       <c r="D134" t="s">
+        <v>419</v>
+      </c>
+      <c r="E134" t="s">
+        <v>420</v>
+      </c>
+      <c r="F134" t="s">
+        <v>12</v>
+      </c>
+      <c r="G134" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
         <v>417</v>
       </c>
-      <c r="E134" t="s">
-        <v>408</v>
-      </c>
-      <c r="F134" t="s">
-        <v>418</v>
-      </c>
-      <c r="G134" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="G135" s="2" t="s">
-        <v>410</v>
+      <c r="B135" t="s">
+        <v>422</v>
+      </c>
+      <c r="C135"/>
+      <c r="D135" t="s">
+        <v>423</v>
+      </c>
+      <c r="E135" t="s">
+        <v>424</v>
+      </c>
+      <c r="F135" t="s">
+        <v>62</v>
+      </c>
+      <c r="G135" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B136" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C136"/>
       <c r="D136" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E136" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F136" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G136" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B137" t="s">
-        <v>426</v>
+        <v>77</v>
       </c>
       <c r="C137"/>
       <c r="D137" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E137" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F137" t="s">
-        <v>62</v>
+        <v>430</v>
       </c>
       <c r="G137" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B138" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C138"/>
       <c r="D138" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E138" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F138" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="G138" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B139" t="s">
-        <v>77</v>
+        <v>169</v>
       </c>
       <c r="C139"/>
       <c r="D139" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E139" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F139" t="s">
-        <v>434</v>
+        <v>165</v>
       </c>
       <c r="G139" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B140" t="s">
-        <v>435</v>
+        <v>173</v>
       </c>
       <c r="C140"/>
       <c r="D140" t="s">
@@ -4777,438 +4765,396 @@
         <v>437</v>
       </c>
       <c r="F140" t="s">
-        <v>125</v>
+        <v>438</v>
       </c>
       <c r="G140" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="s">
+      <c r="A141" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="G141" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="B141" t="s">
-        <v>169</v>
-      </c>
-      <c r="C141"/>
-      <c r="D141" t="s">
-        <v>438</v>
-      </c>
-      <c r="E141" t="s">
-        <v>439</v>
-      </c>
-      <c r="F141" t="s">
-        <v>165</v>
-      </c>
-      <c r="G141" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="B142" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C142"/>
       <c r="D142" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E142" t="s">
+        <v>445</v>
+      </c>
+      <c r="F142" t="s">
+        <v>446</v>
+      </c>
+      <c r="G142" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
         <v>442</v>
       </c>
-      <c r="F142" t="s">
-        <v>173</v>
-      </c>
-      <c r="G142" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C143" s="2"/>
-      <c r="D143" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G143" s="2" t="s">
-        <v>425</v>
+      <c r="B143" t="s">
+        <v>448</v>
+      </c>
+      <c r="C143"/>
+      <c r="D143" t="s">
+        <v>449</v>
+      </c>
+      <c r="E143" t="s">
+        <v>450</v>
+      </c>
+      <c r="F143" t="s">
+        <v>446</v>
+      </c>
+      <c r="G143" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="s">
+      <c r="A144" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F144" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="B144" t="s">
+      <c r="G144" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="C144"/>
-      <c r="D144" t="s">
-        <v>448</v>
-      </c>
-      <c r="E144" t="s">
-        <v>449</v>
-      </c>
-      <c r="F144" t="s">
-        <v>450</v>
-      </c>
-      <c r="G144" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B145" t="s">
-        <v>452</v>
-      </c>
-      <c r="C145"/>
+        <v>258</v>
+      </c>
+      <c r="C145" t="s">
+        <v>258</v>
+      </c>
       <c r="D145" t="s">
-        <v>453</v>
+        <v>259</v>
       </c>
       <c r="E145" t="s">
+        <v>260</v>
+      </c>
+      <c r="F145" t="s">
+        <v>455</v>
+      </c>
+      <c r="G145" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
         <v>454</v>
       </c>
-      <c r="F145" t="s">
-        <v>450</v>
-      </c>
-      <c r="G145" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C146" s="2"/>
-      <c r="D146" s="2" t="s">
+      <c r="B146" t="s">
+        <v>282</v>
+      </c>
+      <c r="C146"/>
+      <c r="D146" t="s">
+        <v>457</v>
+      </c>
+      <c r="E146" t="s">
+        <v>458</v>
+      </c>
+      <c r="F146" t="s">
+        <v>279</v>
+      </c>
+      <c r="G146" t="s">
         <v>456</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="G146" s="2" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B147" t="s">
-        <v>258</v>
-      </c>
-      <c r="C147" t="s">
-        <v>258</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="C147"/>
       <c r="D147" t="s">
-        <v>259</v>
+        <v>459</v>
       </c>
       <c r="E147" t="s">
-        <v>260</v>
+        <v>460</v>
       </c>
       <c r="F147" t="s">
-        <v>459</v>
+        <v>251</v>
       </c>
       <c r="G147" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B148" t="s">
-        <v>282</v>
-      </c>
-      <c r="C148"/>
+        <v>328</v>
+      </c>
+      <c r="C148" t="s">
+        <v>328</v>
+      </c>
       <c r="D148" t="s">
-        <v>461</v>
+        <v>329</v>
       </c>
       <c r="E148" t="s">
-        <v>462</v>
+        <v>330</v>
       </c>
       <c r="F148" t="s">
-        <v>279</v>
+        <v>455</v>
       </c>
       <c r="G148" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B149" t="s">
-        <v>254</v>
+        <v>334</v>
       </c>
       <c r="C149"/>
       <c r="D149" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E149" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F149" t="s">
-        <v>251</v>
+        <v>331</v>
       </c>
       <c r="G149" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B150" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C150" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="D150" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="E150" t="s">
-        <v>330</v>
+        <v>81</v>
       </c>
       <c r="F150" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G150" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B151" t="s">
-        <v>334</v>
-      </c>
-      <c r="C151"/>
+        <v>344</v>
+      </c>
+      <c r="C151" t="s">
+        <v>345</v>
+      </c>
       <c r="D151" t="s">
-        <v>465</v>
+        <v>346</v>
       </c>
       <c r="E151" t="s">
-        <v>466</v>
+        <v>81</v>
       </c>
       <c r="F151" t="s">
-        <v>331</v>
+        <v>455</v>
       </c>
       <c r="G151" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B152" t="s">
-        <v>338</v>
-      </c>
-      <c r="C152" t="s">
-        <v>339</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="C152"/>
       <c r="D152" t="s">
-        <v>340</v>
+        <v>464</v>
       </c>
       <c r="E152" t="s">
-        <v>81</v>
+        <v>465</v>
       </c>
       <c r="F152" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G152" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B153" t="s">
-        <v>344</v>
-      </c>
-      <c r="C153" t="s">
-        <v>345</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="C153"/>
       <c r="D153" t="s">
-        <v>346</v>
+        <v>467</v>
       </c>
       <c r="E153" t="s">
-        <v>81</v>
+        <v>468</v>
       </c>
       <c r="F153" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G153" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B154" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C154"/>
       <c r="D154" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E154" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F154" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="G154" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B155" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C155"/>
       <c r="D155" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E155" t="s">
+        <v>475</v>
+      </c>
+      <c r="F155" t="s">
         <v>472</v>
       </c>
-      <c r="F155" t="s">
-        <v>459</v>
-      </c>
       <c r="G155" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B156" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C156"/>
       <c r="D156" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E156" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="F156" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="G156" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B157" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C157"/>
       <c r="D157" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E157" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F157" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="G157" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B158" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C158"/>
       <c r="D158" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E158" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F158" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="G158" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>458</v>
-      </c>
-      <c r="B159" t="s">
-        <v>483</v>
-      </c>
-      <c r="C159"/>
-      <c r="D159" t="s">
-        <v>484</v>
-      </c>
-      <c r="E159" t="s">
-        <v>485</v>
-      </c>
-      <c r="F159" t="s">
-        <v>476</v>
-      </c>
-      <c r="G159" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>458</v>
-      </c>
-      <c r="B160" t="s">
-        <v>486</v>
-      </c>
-      <c r="C160"/>
-      <c r="D160" t="s">
-        <v>487</v>
-      </c>
-      <c r="E160" t="s">
-        <v>488</v>
-      </c>
-      <c r="F160" t="s">
-        <v>476</v>
-      </c>
-      <c r="G160" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>

--- a/output/tables/2025/metadata_variables.xlsx
+++ b/output/tables/2025/metadata_variables.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="488">
   <si>
     <t xml:space="preserve">familia</t>
   </si>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">Indique el o los elementos de seguridad que dispone su vivienda o edificio. Perro u otro animal con fines de protección del inmueble</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_per_pct_cat</t>
+    <t xml:space="preserve">comgen_per_cat</t>
   </si>
   <si>
     <t xml:space="preserve">comgen_medidas_alarma_privada</t>
@@ -617,6 +617,9 @@
     <t xml:space="preserve">Indique el o los elementos de seguridad que dispone su vivienda o edificio. No tenemos ninguna medida de seguridad</t>
   </si>
   <si>
+    <t xml:space="preserve">Excluida de la batería a propósito (D1): quien la marca tiene todas las medidas en 0, así que el conteo le da 0 sin leer esta columna</t>
+  </si>
+  <si>
     <t xml:space="preserve">comgen_medidas_ns</t>
   </si>
   <si>
@@ -626,6 +629,9 @@
     <t xml:space="preserve">Indique el o los elementos de seguridad que dispone su vivienda o edificio. No sabe</t>
   </si>
   <si>
+    <t xml:space="preserve">Marca de no respuesta: fija 88/99 en comgen_per_cat</t>
+  </si>
+  <si>
     <t xml:space="preserve">comgen_medidas_nr</t>
   </si>
   <si>
@@ -644,7 +650,7 @@
     <t xml:space="preserve">¿Cuál/es de las siguientes medidas ha adoptado en conjunto a las personas de su barrio / cuadra / block para sentirse más seguros/as? Tenemos un grupo de WhatsApp u otra red</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_com_pct_cat</t>
+    <t xml:space="preserve">comgen_com_cat</t>
   </si>
   <si>
     <t xml:space="preserve">comgen_vecinos_medidas_vigilancia</t>
@@ -728,6 +734,9 @@
     <t xml:space="preserve">¿Cuál/es de las siguientes medidas ha adoptado en conjunto a las personas de su barrio / cuadra / block para sentirse más seguros/as? No sabe</t>
   </si>
   <si>
+    <t xml:space="preserve">Marca de no respuesta: fija 88/99 en comgen_com_cat</t>
+  </si>
+  <si>
     <t xml:space="preserve">comgen_vecinos_medidas_nr</t>
   </si>
   <si>
@@ -1352,7 +1361,7 @@
     <t xml:space="preserve">C1; C2; C3; C4</t>
   </si>
   <si>
-    <t xml:space="preserve">emper_ep_pct_cat, emper_barrio_pct_cat, emper_casa_pct_cat, perper_delito, comper_pct_cat, comper_gasto, comgen_per_pct_cat, comgen_com_pct_cat</t>
+    <t xml:space="preserve">emper_ep_pct_cat, emper_barrio_pct_cat, emper_casa_pct_cat, perper_delito, comper_pct_cat, comper_gasto, comgen_per_cat, comgen_com_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Resultado del modelo</t>
@@ -1826,7 +1835,7 @@
     <col min="4" max="4" width="245.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="250.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="250.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="71.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="136.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3109,7 +3118,7 @@
       </c>
       <c r="F61"/>
       <c r="G61" t="s">
-        <v>46</v>
+        <v>201</v>
       </c>
     </row>
     <row r="62">
@@ -3117,20 +3126,20 @@
         <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C62" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D62" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E62" t="s">
         <v>81</v>
       </c>
       <c r="F62"/>
       <c r="G62" t="s">
-        <v>46</v>
+        <v>205</v>
       </c>
     </row>
     <row r="63">
@@ -3138,20 +3147,20 @@
         <v>7</v>
       </c>
       <c r="B63" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C63" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D63" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E63" t="s">
         <v>81</v>
       </c>
       <c r="F63"/>
       <c r="G63" t="s">
-        <v>46</v>
+        <v>205</v>
       </c>
     </row>
     <row r="64">
@@ -3159,20 +3168,20 @@
         <v>7</v>
       </c>
       <c r="B64" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C64" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D64" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E64" t="s">
         <v>81</v>
       </c>
       <c r="F64"/>
       <c r="G64" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="65">
@@ -3180,20 +3189,20 @@
         <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C65" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D65" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E65" t="s">
         <v>81</v>
       </c>
       <c r="F65"/>
       <c r="G65" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="66">
@@ -3201,20 +3210,20 @@
         <v>7</v>
       </c>
       <c r="B66" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C66" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D66" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E66" t="s">
         <v>81</v>
       </c>
       <c r="F66"/>
       <c r="G66" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="67">
@@ -3222,20 +3231,20 @@
         <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C67" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D67" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E67" t="s">
         <v>81</v>
       </c>
       <c r="F67"/>
       <c r="G67" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68">
@@ -3243,20 +3252,20 @@
         <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C68" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D68" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E68" t="s">
         <v>81</v>
       </c>
       <c r="F68"/>
       <c r="G68" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69">
@@ -3264,20 +3273,20 @@
         <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C69" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D69" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E69" t="s">
         <v>81</v>
       </c>
       <c r="F69"/>
       <c r="G69" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="70">
@@ -3285,20 +3294,20 @@
         <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C70" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D70" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E70" t="s">
         <v>81</v>
       </c>
       <c r="F70"/>
       <c r="G70" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="71">
@@ -3306,20 +3315,20 @@
         <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C71" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D71" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E71" t="s">
         <v>81</v>
       </c>
       <c r="F71"/>
       <c r="G71" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="72">
@@ -3327,20 +3336,20 @@
         <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C72" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D72" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E72" t="s">
         <v>81</v>
       </c>
       <c r="F72"/>
       <c r="G72" t="s">
-        <v>46</v>
+        <v>201</v>
       </c>
     </row>
     <row r="73">
@@ -3348,20 +3357,20 @@
         <v>7</v>
       </c>
       <c r="B73" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C73" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D73" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E73" t="s">
         <v>81</v>
       </c>
       <c r="F73"/>
       <c r="G73" t="s">
-        <v>46</v>
+        <v>240</v>
       </c>
     </row>
     <row r="74">
@@ -3369,20 +3378,20 @@
         <v>7</v>
       </c>
       <c r="B74" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C74" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D74" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E74" t="s">
         <v>81</v>
       </c>
       <c r="F74"/>
       <c r="G74" t="s">
-        <v>46</v>
+        <v>240</v>
       </c>
     </row>
     <row r="75">
@@ -3390,16 +3399,16 @@
         <v>7</v>
       </c>
       <c r="B75" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C75" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D75" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E75" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F75"/>
       <c r="G75" t="s">
@@ -3411,16 +3420,16 @@
         <v>7</v>
       </c>
       <c r="B76" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C76" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D76" t="s">
+        <v>250</v>
+      </c>
+      <c r="E76" t="s">
         <v>247</v>
-      </c>
-      <c r="E76" t="s">
-        <v>244</v>
       </c>
       <c r="F76"/>
       <c r="G76" t="s">
@@ -3432,16 +3441,16 @@
         <v>7</v>
       </c>
       <c r="B77" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C77" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D77" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E77" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F77"/>
       <c r="G77" t="s">
@@ -3453,20 +3462,20 @@
         <v>7</v>
       </c>
       <c r="B78" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C78" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D78" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E78" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F78"/>
       <c r="G78" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="79">
@@ -3474,16 +3483,16 @@
         <v>7</v>
       </c>
       <c r="B79" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C79" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D79" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E79" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F79"/>
       <c r="G79" t="s">
@@ -3495,20 +3504,20 @@
         <v>7</v>
       </c>
       <c r="B80" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C80" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D80" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E80" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F80"/>
       <c r="G80" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="81">
@@ -3516,16 +3525,16 @@
         <v>7</v>
       </c>
       <c r="B81" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C81" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E81" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F81"/>
       <c r="G81" t="s">
@@ -3537,16 +3546,16 @@
         <v>7</v>
       </c>
       <c r="B82" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C82" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D82" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E82" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F82"/>
       <c r="G82" t="s">
@@ -3558,13 +3567,13 @@
         <v>7</v>
       </c>
       <c r="B83" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C83" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D83" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E83" t="s">
         <v>76</v>
@@ -3579,16 +3588,16 @@
         <v>7</v>
       </c>
       <c r="B84" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C84" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D84" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E84" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F84"/>
       <c r="G84" t="s">
@@ -3600,16 +3609,16 @@
         <v>7</v>
       </c>
       <c r="B85" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C85" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D85" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E85" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F85"/>
       <c r="G85" t="s">
@@ -3621,16 +3630,16 @@
         <v>7</v>
       </c>
       <c r="B86" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C86" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D86" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E86" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F86"/>
       <c r="G86" t="s">
@@ -3642,20 +3651,20 @@
         <v>7</v>
       </c>
       <c r="B87" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C87" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D87" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E87" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F87"/>
       <c r="G87" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="88">
@@ -3663,16 +3672,16 @@
         <v>7</v>
       </c>
       <c r="B88" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C88" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D88" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E88" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F88"/>
       <c r="G88" t="s">
@@ -3684,16 +3693,16 @@
         <v>7</v>
       </c>
       <c r="B89" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C89" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D89" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E89" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F89"/>
       <c r="G89" t="s">
@@ -3705,16 +3714,16 @@
         <v>7</v>
       </c>
       <c r="B90" t="s">
+        <v>291</v>
+      </c>
+      <c r="C90" t="s">
+        <v>291</v>
+      </c>
+      <c r="D90" t="s">
+        <v>292</v>
+      </c>
+      <c r="E90" t="s">
         <v>288</v>
-      </c>
-      <c r="C90" t="s">
-        <v>288</v>
-      </c>
-      <c r="D90" t="s">
-        <v>289</v>
-      </c>
-      <c r="E90" t="s">
-        <v>285</v>
       </c>
       <c r="F90"/>
       <c r="G90" t="s">
@@ -3726,16 +3735,16 @@
         <v>7</v>
       </c>
       <c r="B91" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C91" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D91" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E91" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F91"/>
       <c r="G91" t="s">
@@ -3747,16 +3756,16 @@
         <v>7</v>
       </c>
       <c r="B92" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C92" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D92" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E92" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F92"/>
       <c r="G92" t="s">
@@ -3768,16 +3777,16 @@
         <v>7</v>
       </c>
       <c r="B93" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C93" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D93" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E93" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F93"/>
       <c r="G93" t="s">
@@ -3789,16 +3798,16 @@
         <v>7</v>
       </c>
       <c r="B94" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C94" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D94" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E94" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F94"/>
       <c r="G94" t="s">
@@ -3810,16 +3819,16 @@
         <v>7</v>
       </c>
       <c r="B95" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C95" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D95" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E95" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F95"/>
       <c r="G95" t="s">
@@ -3831,16 +3840,16 @@
         <v>7</v>
       </c>
       <c r="B96" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C96" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D96" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E96" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F96"/>
       <c r="G96" t="s">
@@ -3852,16 +3861,16 @@
         <v>7</v>
       </c>
       <c r="B97" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C97" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D97" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E97" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F97"/>
       <c r="G97" t="s">
@@ -3873,16 +3882,16 @@
         <v>7</v>
       </c>
       <c r="B98" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C98" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D98" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E98" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F98"/>
       <c r="G98" t="s">
@@ -3894,16 +3903,16 @@
         <v>7</v>
       </c>
       <c r="B99" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C99" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D99" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E99" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F99"/>
       <c r="G99" t="s">
@@ -3915,16 +3924,16 @@
         <v>7</v>
       </c>
       <c r="B100" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C100" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D100" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E100" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F100"/>
       <c r="G100" t="s">
@@ -3936,16 +3945,16 @@
         <v>7</v>
       </c>
       <c r="B101" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C101" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D101" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E101" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F101"/>
       <c r="G101" t="s">
@@ -3957,16 +3966,16 @@
         <v>7</v>
       </c>
       <c r="B102" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C102" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D102" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E102" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F102"/>
       <c r="G102" t="s">
@@ -3978,16 +3987,16 @@
         <v>7</v>
       </c>
       <c r="B103" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C103" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D103" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E103" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F103"/>
       <c r="G103" t="s">
@@ -3999,16 +4008,16 @@
         <v>7</v>
       </c>
       <c r="B104" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C104" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D104" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E104" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F104"/>
       <c r="G104" t="s">
@@ -4020,13 +4029,13 @@
         <v>7</v>
       </c>
       <c r="B105" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C105" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D105" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E105" t="s">
         <v>81</v>
@@ -4041,20 +4050,20 @@
         <v>7</v>
       </c>
       <c r="B106" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C106" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D106" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E106" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F106"/>
       <c r="G106" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="107">
@@ -4062,20 +4071,20 @@
         <v>7</v>
       </c>
       <c r="B107" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C107" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D107" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E107" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F107"/>
       <c r="G107" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="108">
@@ -4083,13 +4092,13 @@
         <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C108" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D108" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E108" t="s">
         <v>81</v>
@@ -4104,20 +4113,20 @@
         <v>7</v>
       </c>
       <c r="B109" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C109" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D109" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E109" t="s">
         <v>81</v>
       </c>
       <c r="F109"/>
       <c r="G109" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="110">
@@ -4125,13 +4134,13 @@
         <v>7</v>
       </c>
       <c r="B110" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C110" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D110" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E110" t="s">
         <v>81</v>
@@ -4146,20 +4155,20 @@
         <v>7</v>
       </c>
       <c r="B111" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C111" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D111" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E111" t="s">
         <v>81</v>
       </c>
       <c r="F111"/>
       <c r="G111" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="112">
@@ -4167,20 +4176,20 @@
         <v>7</v>
       </c>
       <c r="B112" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C112" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D112" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E112" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F112"/>
       <c r="G112" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="113">
@@ -4188,20 +4197,20 @@
         <v>7</v>
       </c>
       <c r="B113" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C113" t="s">
+        <v>356</v>
+      </c>
+      <c r="D113" t="s">
+        <v>357</v>
+      </c>
+      <c r="E113" t="s">
         <v>353</v>
-      </c>
-      <c r="D113" t="s">
-        <v>354</v>
-      </c>
-      <c r="E113" t="s">
-        <v>350</v>
       </c>
       <c r="F113"/>
       <c r="G113" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="114">
@@ -4209,20 +4218,20 @@
         <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C114" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D114" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E114" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F114"/>
       <c r="G114" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="115">
@@ -4230,20 +4239,20 @@
         <v>7</v>
       </c>
       <c r="B115" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C115" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D115" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E115" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F115"/>
       <c r="G115" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="116">
@@ -4251,20 +4260,20 @@
         <v>7</v>
       </c>
       <c r="B116" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C116" t="s">
+        <v>367</v>
+      </c>
+      <c r="D116" t="s">
+        <v>368</v>
+      </c>
+      <c r="E116" t="s">
         <v>364</v>
-      </c>
-      <c r="D116" t="s">
-        <v>365</v>
-      </c>
-      <c r="E116" t="s">
-        <v>361</v>
       </c>
       <c r="F116"/>
       <c r="G116" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="117">
@@ -4272,20 +4281,20 @@
         <v>7</v>
       </c>
       <c r="B117" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C117" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D117" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E117" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F117"/>
       <c r="G117" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="118">
@@ -4293,20 +4302,20 @@
         <v>7</v>
       </c>
       <c r="B118" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C118" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D118" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E118" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F118"/>
       <c r="G118" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="119">
@@ -4314,20 +4323,20 @@
         <v>7</v>
       </c>
       <c r="B119" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C119" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D119" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E119" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F119"/>
       <c r="G119" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="120">
@@ -4335,20 +4344,20 @@
         <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C120" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D120" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E120" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F120"/>
       <c r="G120" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="121">
@@ -4356,20 +4365,20 @@
         <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C121" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D121" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E121" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F121"/>
       <c r="G121" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="122">
@@ -4377,20 +4386,20 @@
         <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C122" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D122" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E122" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F122"/>
       <c r="G122" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="123">
@@ -4398,20 +4407,20 @@
         <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E123" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F123"/>
       <c r="G123" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124">
@@ -4419,20 +4428,20 @@
         <v>7</v>
       </c>
       <c r="B124" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C124" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D124" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E124" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F124"/>
       <c r="G124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125">
@@ -4440,20 +4449,20 @@
         <v>7</v>
       </c>
       <c r="B125" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C125" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D125" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E125" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F125"/>
       <c r="G125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126">
@@ -4461,20 +4470,20 @@
         <v>7</v>
       </c>
       <c r="B126" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C126" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D126" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E126" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F126"/>
       <c r="G126" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127">
@@ -4482,20 +4491,20 @@
         <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C127" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D127" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E127" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F127"/>
       <c r="G127" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128">
@@ -4503,20 +4512,20 @@
         <v>7</v>
       </c>
       <c r="B128" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C128" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D128" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E128" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F128"/>
       <c r="G128" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="129">
@@ -4524,637 +4533,637 @@
         <v>7</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F129" s="2"/>
       <c r="G129" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B130" t="s">
         <v>12</v>
       </c>
       <c r="C130"/>
       <c r="D130" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E130" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F130" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G130" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B131" t="s">
         <v>62</v>
       </c>
       <c r="C131"/>
       <c r="D131" t="s">
+        <v>414</v>
+      </c>
+      <c r="E131" t="s">
         <v>411</v>
       </c>
-      <c r="E131" t="s">
-        <v>408</v>
-      </c>
       <c r="F131" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="G131" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B132" t="s">
         <v>69</v>
       </c>
       <c r="C132"/>
       <c r="D132" t="s">
+        <v>416</v>
+      </c>
+      <c r="E132" t="s">
+        <v>411</v>
+      </c>
+      <c r="F132" t="s">
+        <v>417</v>
+      </c>
+      <c r="G132" t="s">
         <v>413</v>
-      </c>
-      <c r="E132" t="s">
-        <v>408</v>
-      </c>
-      <c r="F132" t="s">
-        <v>414</v>
-      </c>
-      <c r="G132" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B134" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C134"/>
       <c r="D134" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E134" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F134" t="s">
         <v>12</v>
       </c>
       <c r="G134" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B135" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C135"/>
       <c r="D135" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E135" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F135" t="s">
         <v>62</v>
       </c>
       <c r="G135" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B136" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C136"/>
       <c r="D136" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E136" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F136" t="s">
         <v>69</v>
       </c>
       <c r="G136" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B137" t="s">
         <v>77</v>
       </c>
       <c r="C137"/>
       <c r="D137" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E137" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F137" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="G137" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B138" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C138"/>
       <c r="D138" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E138" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F138" t="s">
         <v>125</v>
       </c>
       <c r="G138" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B139" t="s">
         <v>169</v>
       </c>
       <c r="C139"/>
       <c r="D139" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E139" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F139" t="s">
         <v>165</v>
       </c>
       <c r="G139" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B140" t="s">
         <v>173</v>
       </c>
       <c r="C140"/>
       <c r="D140" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E140" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F140" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G140" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B142" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C142"/>
       <c r="D142" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E142" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F142" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="G142" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B143" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C143"/>
       <c r="D143" t="s">
+        <v>452</v>
+      </c>
+      <c r="E143" t="s">
+        <v>453</v>
+      </c>
+      <c r="F143" t="s">
         <v>449</v>
       </c>
-      <c r="E143" t="s">
+      <c r="G143" t="s">
         <v>450</v>
-      </c>
-      <c r="F143" t="s">
-        <v>446</v>
-      </c>
-      <c r="G143" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B145" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C145" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D145" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E145" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F145" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="G145" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B146" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C146"/>
       <c r="D146" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E146" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F146" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="G146" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B147" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C147"/>
       <c r="D147" t="s">
+        <v>462</v>
+      </c>
+      <c r="E147" t="s">
+        <v>463</v>
+      </c>
+      <c r="F147" t="s">
+        <v>254</v>
+      </c>
+      <c r="G147" t="s">
         <v>459</v>
-      </c>
-      <c r="E147" t="s">
-        <v>460</v>
-      </c>
-      <c r="F147" t="s">
-        <v>251</v>
-      </c>
-      <c r="G147" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B148" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C148" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D148" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E148" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F148" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="G148" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B149" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C149"/>
       <c r="D149" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E149" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F149" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G149" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B150" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C150" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D150" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E150" t="s">
         <v>81</v>
       </c>
       <c r="F150" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="G150" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B151" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C151" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D151" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E151" t="s">
         <v>81</v>
       </c>
       <c r="F151" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="G151" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B152" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C152"/>
       <c r="D152" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E152" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F152" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="G152" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B153" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C153"/>
       <c r="D153" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E153" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F153" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="G153" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B154" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C154"/>
       <c r="D154" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E154" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F154" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G154" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B155" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C155"/>
       <c r="D155" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E155" t="s">
+        <v>478</v>
+      </c>
+      <c r="F155" t="s">
         <v>475</v>
       </c>
-      <c r="F155" t="s">
-        <v>472</v>
-      </c>
       <c r="G155" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B156" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C156"/>
       <c r="D156" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E156" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F156" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G156" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B157" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C157"/>
       <c r="D157" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E157" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="F157" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G157" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B158" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C158"/>
       <c r="D158" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E158" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="F158" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G158" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>

--- a/output/tables/2025/metadata_variables.xlsx
+++ b/output/tables/2025/metadata_variables.xlsx
@@ -617,7 +617,7 @@
     <t xml:space="preserve">Indique el o los elementos de seguridad que dispone su vivienda o edificio. No tenemos ninguna medida de seguridad</t>
   </si>
   <si>
-    <t xml:space="preserve">Excluida de la batería a propósito (D1): quien la marca tiene todas las medidas en 0, así que el conteo le da 0 sin leer esta columna</t>
+    <t xml:space="preserve">Excluida de la batería a propósito: quien la marca tiene todas las medidas en 0, así que el conteo le da 0 sin leer esta columna</t>
   </si>
   <si>
     <t xml:space="preserve">comgen_medidas_ns</t>
@@ -1835,7 +1835,7 @@
     <col min="4" max="4" width="245.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="250.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="250.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="136.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="131.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/output/tables/2025/metadata_variables.xlsx
+++ b/output/tables/2025/metadata_variables.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="498">
   <si>
     <t xml:space="preserve">familia</t>
   </si>
@@ -1239,6 +1239,36 @@
   </si>
   <si>
     <t xml:space="preserve">Durante los últimos doce meses ¿con qué frecuencia diría usted que suceden las siguientes situaciones delictivas en su barrio? Balaceras o disparos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_aumento_pais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_AUMENTO_PAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pensando en la delincuencia, usted diría que durante los últimos doce meses, la delincuencia en el PAÍS...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = Aumentó; 2 = Se mantuvo; 3 = Disminuyó; 88 = No sabe; 96 = Sin dato; 99 = No responde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_aumento_com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_AUMENTO_COM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pensando en la delincuencia, usted diría que durante los últimos doce meses, la delincuencia en su COMUNA...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_aumento_barrio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_AUMENTO_BARRIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pensando en la delincuencia, usted diría que durante los últimos doce meses, la delincuencia en su BARRIO...</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente: índice</t>
@@ -4529,284 +4559,284 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B129" s="2" t="s">
+      <c r="A129" t="s">
+        <v>7</v>
+      </c>
+      <c r="B129" t="s">
         <v>406</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="C129" t="s">
         <v>407</v>
       </c>
-      <c r="D129" s="2" t="s">
+      <c r="D129" t="s">
         <v>408</v>
       </c>
-      <c r="E129" s="2" t="s">
+      <c r="E129" t="s">
         <v>364</v>
       </c>
-      <c r="F129" s="2"/>
-      <c r="G129" s="2" t="s">
+      <c r="F129"/>
+      <c r="G129" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
+        <v>7</v>
+      </c>
+      <c r="B130" t="s">
         <v>409</v>
       </c>
-      <c r="B130" t="s">
-        <v>12</v>
-      </c>
-      <c r="C130"/>
+      <c r="C130" t="s">
+        <v>410</v>
+      </c>
       <c r="D130" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E130" t="s">
-        <v>411</v>
-      </c>
-      <c r="F130" t="s">
         <v>412</v>
       </c>
+      <c r="F130"/>
       <c r="G130" t="s">
-        <v>413</v>
+        <v>264</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>409</v>
+        <v>7</v>
       </c>
       <c r="B131" t="s">
-        <v>62</v>
-      </c>
-      <c r="C131"/>
+        <v>413</v>
+      </c>
+      <c r="C131" t="s">
+        <v>414</v>
+      </c>
       <c r="D131" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E131" t="s">
-        <v>411</v>
-      </c>
-      <c r="F131" t="s">
-        <v>415</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="F131"/>
       <c r="G131" t="s">
-        <v>413</v>
+        <v>264</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="s">
-        <v>409</v>
-      </c>
-      <c r="B132" t="s">
-        <v>69</v>
-      </c>
-      <c r="C132"/>
-      <c r="D132" t="s">
+      <c r="A132" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="E132" t="s">
-        <v>411</v>
-      </c>
-      <c r="F132" t="s">
+      <c r="C132" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="G132" t="s">
-        <v>413</v>
+      <c r="D132" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F132" s="2"/>
+      <c r="G132" s="2" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="F133" s="2" t="s">
+      <c r="A133" t="s">
         <v>419</v>
       </c>
-      <c r="G133" s="2" t="s">
-        <v>413</v>
+      <c r="B133" t="s">
+        <v>12</v>
+      </c>
+      <c r="C133"/>
+      <c r="D133" t="s">
+        <v>420</v>
+      </c>
+      <c r="E133" t="s">
+        <v>421</v>
+      </c>
+      <c r="F133" t="s">
+        <v>422</v>
+      </c>
+      <c r="G133" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B134" t="s">
-        <v>421</v>
+        <v>62</v>
       </c>
       <c r="C134"/>
       <c r="D134" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E134" t="s">
+        <v>421</v>
+      </c>
+      <c r="F134" t="s">
+        <v>425</v>
+      </c>
+      <c r="G134" t="s">
         <v>423</v>
-      </c>
-      <c r="F134" t="s">
-        <v>12</v>
-      </c>
-      <c r="G134" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B135" t="s">
-        <v>425</v>
+        <v>69</v>
       </c>
       <c r="C135"/>
       <c r="D135" t="s">
         <v>426</v>
       </c>
       <c r="E135" t="s">
+        <v>421</v>
+      </c>
+      <c r="F135" t="s">
         <v>427</v>
       </c>
-      <c r="F135" t="s">
-        <v>62</v>
-      </c>
       <c r="G135" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="s">
-        <v>420</v>
-      </c>
-      <c r="B136" t="s">
+      <c r="A136" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="C136"/>
-      <c r="D136" t="s">
+      <c r="E136" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F136" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="E136" t="s">
-        <v>430</v>
-      </c>
-      <c r="F136" t="s">
-        <v>69</v>
-      </c>
-      <c r="G136" t="s">
-        <v>424</v>
+      <c r="G136" s="2" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="B137" t="s">
-        <v>77</v>
+        <v>431</v>
       </c>
       <c r="C137"/>
       <c r="D137" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E137" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F137" t="s">
-        <v>433</v>
+        <v>12</v>
       </c>
       <c r="G137" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="B138" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C138"/>
       <c r="D138" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E138" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F138" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="G138" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="B139" t="s">
-        <v>169</v>
+        <v>438</v>
       </c>
       <c r="C139"/>
       <c r="D139" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E139" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F139" t="s">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="G139" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="B140" t="s">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="C140"/>
       <c r="D140" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E140" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F140" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="G140" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C141" s="2"/>
-      <c r="D141" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="F141" s="2" t="s">
+      <c r="A141" t="s">
+        <v>430</v>
+      </c>
+      <c r="B141" t="s">
         <v>444</v>
       </c>
-      <c r="G141" s="2" t="s">
-        <v>424</v>
+      <c r="C141"/>
+      <c r="D141" t="s">
+        <v>445</v>
+      </c>
+      <c r="E141" t="s">
+        <v>446</v>
+      </c>
+      <c r="F141" t="s">
+        <v>125</v>
+      </c>
+      <c r="G141" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="B142" t="s">
-        <v>446</v>
+        <v>169</v>
       </c>
       <c r="C142"/>
       <c r="D142" t="s">
@@ -4816,275 +4846,275 @@
         <v>448</v>
       </c>
       <c r="F142" t="s">
-        <v>449</v>
+        <v>165</v>
       </c>
       <c r="G142" t="s">
-        <v>450</v>
+        <v>434</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="B143" t="s">
-        <v>451</v>
+        <v>173</v>
       </c>
       <c r="C143"/>
       <c r="D143" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E143" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F143" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G143" t="s">
-        <v>450</v>
+        <v>434</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>454</v>
+        <v>212</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>450</v>
+        <v>434</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
+        <v>455</v>
+      </c>
+      <c r="B145" t="s">
+        <v>456</v>
+      </c>
+      <c r="C145"/>
+      <c r="D145" t="s">
         <v>457</v>
       </c>
-      <c r="B145" t="s">
-        <v>261</v>
-      </c>
-      <c r="C145" t="s">
-        <v>261</v>
-      </c>
-      <c r="D145" t="s">
-        <v>262</v>
-      </c>
       <c r="E145" t="s">
-        <v>263</v>
+        <v>458</v>
       </c>
       <c r="F145" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G145" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B146" t="s">
-        <v>285</v>
+        <v>461</v>
       </c>
       <c r="C146"/>
       <c r="D146" t="s">
+        <v>462</v>
+      </c>
+      <c r="E146" t="s">
+        <v>463</v>
+      </c>
+      <c r="F146" t="s">
+        <v>459</v>
+      </c>
+      <c r="G146" t="s">
         <v>460</v>
       </c>
-      <c r="E146" t="s">
-        <v>461</v>
-      </c>
-      <c r="F146" t="s">
-        <v>282</v>
-      </c>
-      <c r="G146" t="s">
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="F147" s="2" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>457</v>
-      </c>
-      <c r="B147" t="s">
-        <v>257</v>
-      </c>
-      <c r="C147"/>
-      <c r="D147" t="s">
-        <v>462</v>
-      </c>
-      <c r="E147" t="s">
-        <v>463</v>
-      </c>
-      <c r="F147" t="s">
-        <v>254</v>
-      </c>
-      <c r="G147" t="s">
-        <v>459</v>
+      <c r="G147" s="2" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B148" t="s">
-        <v>331</v>
+        <v>261</v>
       </c>
       <c r="C148" t="s">
-        <v>331</v>
+        <v>261</v>
       </c>
       <c r="D148" t="s">
-        <v>332</v>
+        <v>262</v>
       </c>
       <c r="E148" t="s">
-        <v>333</v>
+        <v>263</v>
       </c>
       <c r="F148" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="G148" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B149" t="s">
-        <v>337</v>
+        <v>285</v>
       </c>
       <c r="C149"/>
       <c r="D149" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="E149" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="F149" t="s">
-        <v>334</v>
+        <v>282</v>
       </c>
       <c r="G149" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B150" t="s">
-        <v>341</v>
-      </c>
-      <c r="C150" t="s">
-        <v>342</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C150"/>
       <c r="D150" t="s">
-        <v>343</v>
+        <v>472</v>
       </c>
       <c r="E150" t="s">
-        <v>81</v>
+        <v>473</v>
       </c>
       <c r="F150" t="s">
-        <v>458</v>
+        <v>254</v>
       </c>
       <c r="G150" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B151" t="s">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="C151" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="D151" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="E151" t="s">
-        <v>81</v>
+        <v>333</v>
       </c>
       <c r="F151" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="G151" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B152" t="s">
-        <v>466</v>
+        <v>337</v>
       </c>
       <c r="C152"/>
       <c r="D152" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="E152" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="F152" t="s">
-        <v>458</v>
+        <v>334</v>
       </c>
       <c r="G152" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B153" t="s">
+        <v>341</v>
+      </c>
+      <c r="C153" t="s">
+        <v>342</v>
+      </c>
+      <c r="D153" t="s">
+        <v>343</v>
+      </c>
+      <c r="E153" t="s">
+        <v>81</v>
+      </c>
+      <c r="F153" t="s">
+        <v>468</v>
+      </c>
+      <c r="G153" t="s">
         <v>469</v>
-      </c>
-      <c r="C153"/>
-      <c r="D153" t="s">
-        <v>470</v>
-      </c>
-      <c r="E153" t="s">
-        <v>471</v>
-      </c>
-      <c r="F153" t="s">
-        <v>458</v>
-      </c>
-      <c r="G153" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B154" t="s">
-        <v>472</v>
-      </c>
-      <c r="C154"/>
+        <v>347</v>
+      </c>
+      <c r="C154" t="s">
+        <v>348</v>
+      </c>
       <c r="D154" t="s">
-        <v>473</v>
+        <v>349</v>
       </c>
       <c r="E154" t="s">
-        <v>474</v>
+        <v>81</v>
       </c>
       <c r="F154" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="G154" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B155" t="s">
         <v>476</v>
@@ -5097,15 +5127,15 @@
         <v>478</v>
       </c>
       <c r="F155" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="G155" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B156" t="s">
         <v>479</v>
@@ -5118,52 +5148,184 @@
         <v>481</v>
       </c>
       <c r="F156" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="G156" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B157" t="s">
-        <v>482</v>
-      </c>
-      <c r="C157"/>
+        <v>409</v>
+      </c>
+      <c r="C157" t="s">
+        <v>410</v>
+      </c>
       <c r="D157" t="s">
-        <v>483</v>
+        <v>411</v>
       </c>
       <c r="E157" t="s">
-        <v>484</v>
+        <v>412</v>
       </c>
       <c r="F157" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="G157" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B158" t="s">
+        <v>413</v>
+      </c>
+      <c r="C158" t="s">
+        <v>414</v>
+      </c>
+      <c r="D158" t="s">
+        <v>415</v>
+      </c>
+      <c r="E158" t="s">
+        <v>412</v>
+      </c>
+      <c r="F158" t="s">
+        <v>468</v>
+      </c>
+      <c r="G158" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>467</v>
+      </c>
+      <c r="B159" t="s">
+        <v>416</v>
+      </c>
+      <c r="C159" t="s">
+        <v>417</v>
+      </c>
+      <c r="D159" t="s">
+        <v>418</v>
+      </c>
+      <c r="E159" t="s">
+        <v>412</v>
+      </c>
+      <c r="F159" t="s">
+        <v>468</v>
+      </c>
+      <c r="G159" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>467</v>
+      </c>
+      <c r="B160" t="s">
+        <v>482</v>
+      </c>
+      <c r="C160"/>
+      <c r="D160" t="s">
+        <v>483</v>
+      </c>
+      <c r="E160" t="s">
+        <v>484</v>
+      </c>
+      <c r="F160" t="s">
         <v>485</v>
       </c>
-      <c r="C158"/>
-      <c r="D158" t="s">
+      <c r="G160" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>467</v>
+      </c>
+      <c r="B161" t="s">
         <v>486</v>
       </c>
-      <c r="E158" t="s">
+      <c r="C161"/>
+      <c r="D161" t="s">
         <v>487</v>
       </c>
-      <c r="F158" t="s">
-        <v>475</v>
-      </c>
-      <c r="G158" t="s">
-        <v>459</v>
+      <c r="E161" t="s">
+        <v>488</v>
+      </c>
+      <c r="F161" t="s">
+        <v>485</v>
+      </c>
+      <c r="G161" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>467</v>
+      </c>
+      <c r="B162" t="s">
+        <v>489</v>
+      </c>
+      <c r="C162"/>
+      <c r="D162" t="s">
+        <v>490</v>
+      </c>
+      <c r="E162" t="s">
+        <v>491</v>
+      </c>
+      <c r="F162" t="s">
+        <v>485</v>
+      </c>
+      <c r="G162" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>467</v>
+      </c>
+      <c r="B163" t="s">
+        <v>492</v>
+      </c>
+      <c r="C163"/>
+      <c r="D163" t="s">
+        <v>493</v>
+      </c>
+      <c r="E163" t="s">
+        <v>494</v>
+      </c>
+      <c r="F163" t="s">
+        <v>485</v>
+      </c>
+      <c r="G163" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>467</v>
+      </c>
+      <c r="B164" t="s">
+        <v>495</v>
+      </c>
+      <c r="C164"/>
+      <c r="D164" t="s">
+        <v>496</v>
+      </c>
+      <c r="E164" t="s">
+        <v>497</v>
+      </c>
+      <c r="F164" t="s">
+        <v>485</v>
+      </c>
+      <c r="G164" t="s">
+        <v>469</v>
       </c>
     </row>
   </sheetData>
